--- a/assets/operator_ids.xlsx
+++ b/assets/operator_ids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GWE\git\gy454xe-decomp\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CE7499-D201-402B-A6DC-FB762B94AFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9CB61F-8210-45C5-8CCE-937CF2D3F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2E85BE9C-B289-4076-84C1-7CA2746D82AC}"/>
   </bookViews>
@@ -348,9 +348,6 @@
     <t>Divide</t>
   </si>
   <si>
-    <t>Matrix dot product</t>
-  </si>
-  <si>
     <t>Complex angle</t>
   </si>
   <si>
@@ -736,9 +733,6 @@
   </si>
   <si>
     <t>Cube</t>
-  </si>
-  <si>
-    <t>Multiply / Matrix cross product</t>
   </si>
   <si>
     <t>Percentage (divide by 100)</t>
@@ -795,6 +789,12 @@
   </si>
   <si>
     <t>Only used internally. Later set to multiply.</t>
+  </si>
+  <si>
+    <t>Vector dot product</t>
+  </si>
+  <si>
+    <t>Multiply / Vector cross product</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1299,7 @@
         <v>0x3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>11</v>
@@ -1871,7 +1871,7 @@
         <v>0x21</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>49</v>
@@ -1892,7 +1892,7 @@
         <v>0x22</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>50</v>
@@ -1934,7 +1934,7 @@
         <v>0x24</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>49</v>
@@ -1953,7 +1953,7 @@
         <v>0x25</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>50</v>
@@ -2105,7 +2105,7 @@
         <v>0x2D</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>90</v>
@@ -2143,7 +2143,7 @@
         <v>0x2F</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>104</v>
+        <v>248</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>92</v>
@@ -2162,7 +2162,7 @@
         <v>0x30</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>93</v>
@@ -2181,7 +2181,7 @@
         <v>0x31</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>94</v>
@@ -2200,7 +2200,7 @@
         <v>0x32</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>95</v>
@@ -2219,13 +2219,13 @@
         <v>0x33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F53" s="1"/>
     </row>
@@ -2238,13 +2238,13 @@
         <v>0x34</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F54" s="1"/>
     </row>
@@ -2257,13 +2257,13 @@
         <v>0x35</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F55" s="1"/>
     </row>
@@ -2276,13 +2276,13 @@
         <v>0x36</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="1"/>
     </row>
@@ -2295,13 +2295,13 @@
         <v>0x37</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F57" s="1"/>
     </row>
@@ -2314,13 +2314,13 @@
         <v>0x38</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F58" s="1"/>
     </row>
@@ -2333,13 +2333,13 @@
         <v>0x39</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F59" s="1"/>
     </row>
@@ -2352,13 +2352,13 @@
         <v>0x3A</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F60" s="1"/>
     </row>
@@ -2371,13 +2371,13 @@
         <v>0x3B</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" s="1"/>
     </row>
@@ -2390,13 +2390,13 @@
         <v>0x3C</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="1"/>
     </row>
@@ -2409,13 +2409,13 @@
         <v>0x3D</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F63" s="1"/>
     </row>
@@ -2428,13 +2428,13 @@
         <v>0x3E</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F64" s="1"/>
     </row>
@@ -2447,13 +2447,13 @@
         <v>0x3F</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F65" s="1"/>
     </row>
@@ -2466,13 +2466,13 @@
         <v>0x40</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F66" s="1"/>
     </row>
@@ -2485,13 +2485,13 @@
         <v>0x41</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F67" s="1"/>
     </row>
@@ -2504,13 +2504,13 @@
         <v>0x42</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F68" s="1"/>
     </row>
@@ -2523,13 +2523,13 @@
         <v>0x43</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F69" s="1"/>
     </row>
@@ -2542,13 +2542,13 @@
         <v>0x44</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F70" s="1"/>
     </row>
@@ -2561,13 +2561,13 @@
         <v>0x45</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F71" s="1"/>
     </row>
@@ -2580,13 +2580,13 @@
         <v>0x46</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F72" s="1"/>
     </row>
@@ -2599,13 +2599,13 @@
         <v>0x47</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F73" s="1"/>
     </row>
@@ -2618,13 +2618,13 @@
         <v>0x48</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F74" s="1"/>
     </row>
@@ -2637,13 +2637,13 @@
         <v>0x49</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F75" s="1"/>
     </row>
@@ -2656,13 +2656,13 @@
         <v>0x4A</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F76" s="1"/>
     </row>
@@ -2675,13 +2675,13 @@
         <v>0x4B</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F77" s="1"/>
     </row>
@@ -2694,13 +2694,13 @@
         <v>0x4C</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F78" s="1"/>
     </row>
@@ -2713,13 +2713,13 @@
         <v>0x4D</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F79" s="1"/>
     </row>
@@ -2732,13 +2732,13 @@
         <v>0x4E</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F80" s="1"/>
     </row>
@@ -2751,13 +2751,13 @@
         <v>0x4F</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F81" s="1"/>
     </row>
@@ -2770,13 +2770,13 @@
         <v>0x50</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F82" s="1"/>
     </row>
@@ -2789,13 +2789,13 @@
         <v>0x51</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F83" s="1"/>
     </row>
@@ -2808,13 +2808,13 @@
         <v>0x52</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F84" s="1"/>
     </row>
@@ -2827,13 +2827,13 @@
         <v>0x53</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F85" s="1"/>
     </row>
@@ -2846,13 +2846,13 @@
         <v>0x54</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F86" s="1"/>
     </row>
@@ -2865,13 +2865,13 @@
         <v>0x55</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F87" s="1"/>
     </row>
@@ -2884,13 +2884,13 @@
         <v>0x56</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F88" s="1"/>
     </row>
@@ -2903,13 +2903,13 @@
         <v>0x57</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F89" s="1"/>
     </row>
@@ -2922,13 +2922,13 @@
         <v>0x58</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F90" s="1"/>
     </row>
@@ -2941,13 +2941,13 @@
         <v>0x59</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F91" s="1"/>
     </row>
@@ -2960,13 +2960,13 @@
         <v>0x5A</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F92" s="1"/>
     </row>
@@ -2979,13 +2979,13 @@
         <v>0x5B</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F93" s="1"/>
     </row>
@@ -2998,13 +2998,13 @@
         <v>0x5C</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F94" s="1"/>
     </row>
@@ -3017,13 +3017,13 @@
         <v>0x5D</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F95" s="1"/>
     </row>
@@ -3036,13 +3036,13 @@
         <v>0x5E</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F96" s="1"/>
     </row>
@@ -3055,13 +3055,13 @@
         <v>0x5F</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="F97" s="1"/>
     </row>
@@ -3074,13 +3074,13 @@
         <v>0x60</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F98" s="1"/>
     </row>
@@ -3093,13 +3093,13 @@
         <v>0x61</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F99" s="1"/>
     </row>
@@ -3112,13 +3112,13 @@
         <v>0x62</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F100" s="1"/>
     </row>
@@ -3131,13 +3131,13 @@
         <v>0x63</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F101" s="1"/>
     </row>
@@ -3150,7 +3150,7 @@
         <v>0x64</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>96</v>
@@ -3169,7 +3169,7 @@
         <v>0x65</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>97</v>
@@ -3188,7 +3188,7 @@
         <v>0x66</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>98</v>
@@ -3207,13 +3207,13 @@
         <v>0x67</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F105" s="1"/>
     </row>
@@ -3226,13 +3226,13 @@
         <v>0x68</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F106" s="1"/>
     </row>
@@ -3245,13 +3245,13 @@
         <v>0x69</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F107" s="1"/>
     </row>
@@ -3264,13 +3264,13 @@
         <v>0x6A</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F108" s="1"/>
     </row>
@@ -3283,13 +3283,13 @@
         <v>0x6B</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F109" s="1"/>
     </row>
@@ -3302,13 +3302,13 @@
         <v>0x6C</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F110" s="1"/>
     </row>
@@ -3321,13 +3321,13 @@
         <v>0x6D</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F111" s="1"/>
     </row>
@@ -3340,13 +3340,13 @@
         <v>0x6E</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F112" s="1"/>
     </row>
@@ -3359,13 +3359,13 @@
         <v>0x6F</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F113" s="1"/>
     </row>
@@ -3378,13 +3378,13 @@
         <v>0x70</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F114" s="1"/>
     </row>
@@ -3397,13 +3397,13 @@
         <v>0x71</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F115" s="1"/>
     </row>
@@ -3416,13 +3416,13 @@
         <v>0x72</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F116" s="1"/>
     </row>
@@ -3435,13 +3435,13 @@
         <v>0x73</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F117" s="1"/>
     </row>
@@ -3454,10 +3454,10 @@
         <v>0x74</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>101</v>
@@ -3473,16 +3473,16 @@
         <v>0x75</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3494,13 +3494,13 @@
         <v>0x76</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F120" s="1"/>
     </row>
@@ -3513,10 +3513,10 @@
         <v>0x77</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>14</v>
